--- a/04_Modules/03_Classify/c_data/03_classify.xlsx
+++ b/04_Modules/03_Classify/c_data/03_classify.xlsx
@@ -210,7 +210,7 @@
     <t>modules</t>
   </si>
   <si>
-    <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
+    <t>04_Modules/01_Build/c_data/modules.rds</t>
   </si>
   <si>
     <t>25cd43ced16098e9558525cfe4c1ef5e</t>
